--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/111.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/111.xlsx
@@ -426,13 +426,13 @@
         <v>-6.996689298882249</v>
       </c>
       <c r="E2">
-        <v>-19.26617284711476</v>
+        <v>-19.23761629002239</v>
       </c>
       <c r="F2">
-        <v>-3.528566951726061</v>
+        <v>-3.305942383856291</v>
       </c>
       <c r="G2">
-        <v>-12.25392918500646</v>
+        <v>-12.41506336803941</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.967276271382777</v>
       </c>
       <c r="E3">
-        <v>-20.00229893943162</v>
+        <v>-18.91728109566781</v>
       </c>
       <c r="F3">
-        <v>-3.393926599177238</v>
+        <v>-3.214989299763711</v>
       </c>
       <c r="G3">
-        <v>-12.12410283113841</v>
+        <v>-12.00516486154901</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.91723597719255</v>
       </c>
       <c r="E4">
-        <v>-20.9082382785621</v>
+        <v>-20.6869000544892</v>
       </c>
       <c r="F4">
-        <v>-3.304001519031532</v>
+        <v>-3.224025131393448</v>
       </c>
       <c r="G4">
-        <v>-12.10357744879492</v>
+        <v>-11.46628087975752</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.842258022167825</v>
       </c>
       <c r="E5">
-        <v>-21.17149658652401</v>
+        <v>-20.57519165766799</v>
       </c>
       <c r="F5">
-        <v>-3.497313477985839</v>
+        <v>-3.288366912671094</v>
       </c>
       <c r="G5">
-        <v>-12.27869868673129</v>
+        <v>-12.33337896740343</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.730539553263603</v>
       </c>
       <c r="E6">
-        <v>-21.21563109420277</v>
+        <v>-20.0345235604702</v>
       </c>
       <c r="F6">
-        <v>-3.427388500413324</v>
+        <v>-3.20975733124763</v>
       </c>
       <c r="G6">
-        <v>-12.64552368521024</v>
+        <v>-12.65187000100902</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.565425126974715</v>
       </c>
       <c r="E7">
-        <v>-21.55577836234091</v>
+        <v>-21.43800633882343</v>
       </c>
       <c r="F7">
-        <v>-3.118409944271316</v>
+        <v>-3.203225654276555</v>
       </c>
       <c r="G7">
-        <v>-12.12361287039859</v>
+        <v>-12.32906532656576</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.339759864827009</v>
       </c>
       <c r="E8">
-        <v>-22.24302410621897</v>
+        <v>-21.92874348161264</v>
       </c>
       <c r="F8">
-        <v>-3.379115390015182</v>
+        <v>-2.940034277956888</v>
       </c>
       <c r="G8">
-        <v>-12.19994411889757</v>
+        <v>-12.25453170429461</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.047125597958871</v>
       </c>
       <c r="E9">
-        <v>-22.57916367486033</v>
+        <v>-22.30601517966566</v>
       </c>
       <c r="F9">
-        <v>-3.074196662514296</v>
+        <v>-3.012664703466946</v>
       </c>
       <c r="G9">
-        <v>-12.27954287584381</v>
+        <v>-12.06829696498291</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.679362897251766</v>
       </c>
       <c r="E10">
-        <v>-23.09243450431171</v>
+        <v>-22.46144599303094</v>
       </c>
       <c r="F10">
-        <v>-3.166585307315927</v>
+        <v>-3.313888083983944</v>
       </c>
       <c r="G10">
-        <v>-11.92440741366403</v>
+        <v>-12.21483826327875</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.246094518536875</v>
       </c>
       <c r="E11">
-        <v>-23.82210299269363</v>
+        <v>-22.80893391753551</v>
       </c>
       <c r="F11">
-        <v>-3.192963010523272</v>
+        <v>-3.063120561971464</v>
       </c>
       <c r="G11">
-        <v>-11.77594599895541</v>
+        <v>-11.77889900557644</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.759075659733323</v>
       </c>
       <c r="E12">
-        <v>-24.87346974610644</v>
+        <v>-24.68291155986367</v>
       </c>
       <c r="F12">
-        <v>-3.154073646064044</v>
+        <v>-2.872648246473954</v>
       </c>
       <c r="G12">
-        <v>-11.08894489919139</v>
+        <v>-11.44795369965212</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.232406897223512</v>
       </c>
       <c r="E13">
-        <v>-24.7713707711295</v>
+        <v>-24.95223349452185</v>
       </c>
       <c r="F13">
-        <v>-2.956194897618103</v>
+        <v>-2.702287863149013</v>
       </c>
       <c r="G13">
-        <v>-11.16233969379704</v>
+        <v>-11.47899006408279</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.698603693433736</v>
       </c>
       <c r="E14">
-        <v>-25.30824400710886</v>
+        <v>-25.83868680999733</v>
       </c>
       <c r="F14">
-        <v>-2.962036544542646</v>
+        <v>-2.746756282066096</v>
       </c>
       <c r="G14">
-        <v>-10.65395576805886</v>
+        <v>-10.57648569189437</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.185396303603826</v>
       </c>
       <c r="E15">
-        <v>-26.68996293938122</v>
+        <v>-27.15178124715746</v>
       </c>
       <c r="F15">
-        <v>-2.722298734498441</v>
+        <v>-2.590166678445294</v>
       </c>
       <c r="G15">
-        <v>-10.02097946095021</v>
+        <v>-10.49073925188171</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.716559117291057</v>
       </c>
       <c r="E16">
-        <v>-27.36276737964882</v>
+        <v>-27.70041945860874</v>
       </c>
       <c r="F16">
-        <v>-2.415453224418642</v>
+        <v>-2.447307264525894</v>
       </c>
       <c r="G16">
-        <v>-9.863576262740018</v>
+        <v>-10.40631371953921</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.322682727182128</v>
       </c>
       <c r="E17">
-        <v>-27.60870427453139</v>
+        <v>-27.74942207584574</v>
       </c>
       <c r="F17">
-        <v>-2.430606549318053</v>
+        <v>-2.1229459257139</v>
       </c>
       <c r="G17">
-        <v>-9.578465459806905</v>
+        <v>-9.684604860341478</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.020151144094295</v>
       </c>
       <c r="E18">
-        <v>-28.44382733712993</v>
+        <v>-27.99103880652499</v>
       </c>
       <c r="F18">
-        <v>-2.222981230010774</v>
+        <v>-1.909681909495765</v>
       </c>
       <c r="G18">
-        <v>-8.6834561627194</v>
+        <v>-8.871839446086089</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.815374410711648</v>
       </c>
       <c r="E19">
-        <v>-29.54082073040702</v>
+        <v>-28.62002573229438</v>
       </c>
       <c r="F19">
-        <v>-1.84691154118123</v>
+        <v>-1.774937182654189</v>
       </c>
       <c r="G19">
-        <v>-8.898558859133546</v>
+        <v>-8.844616830116662</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.716738201773315</v>
       </c>
       <c r="E20">
-        <v>-29.84593798785883</v>
+        <v>-30.12994576372389</v>
       </c>
       <c r="F20">
-        <v>-1.940249495026469</v>
+        <v>-1.742044369823826</v>
       </c>
       <c r="G20">
-        <v>-8.416795030076646</v>
+        <v>-8.074997755874593</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.717697110921903</v>
       </c>
       <c r="E21">
-        <v>-30.38909674576084</v>
+        <v>-30.74924854782787</v>
       </c>
       <c r="F21">
-        <v>-1.627700675378396</v>
+        <v>-1.364605389677454</v>
       </c>
       <c r="G21">
-        <v>-8.613454677291511</v>
+        <v>-8.117918978791243</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.805066993637077</v>
       </c>
       <c r="E22">
-        <v>-30.8639208308871</v>
+        <v>-30.96491032973216</v>
       </c>
       <c r="F22">
-        <v>-1.682483096827736</v>
+        <v>-1.201296069685142</v>
       </c>
       <c r="G22">
-        <v>-8.134349216302645</v>
+        <v>-7.547101474727948</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.970193510356541</v>
       </c>
       <c r="E23">
-        <v>-31.96116555447162</v>
+        <v>-30.94706587790493</v>
       </c>
       <c r="F23">
-        <v>-1.395900281787816</v>
+        <v>-1.631988305055287</v>
       </c>
       <c r="G23">
-        <v>-7.977677648656638</v>
+        <v>-7.681099115975488</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.195802406687145</v>
       </c>
       <c r="E24">
-        <v>-31.85519699845513</v>
+        <v>-31.83448149410704</v>
       </c>
       <c r="F24">
-        <v>-1.339880279438694</v>
+        <v>-1.336580892073344</v>
       </c>
       <c r="G24">
-        <v>-8.004896954080525</v>
+        <v>-7.164733464942126</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.464689287743487</v>
       </c>
       <c r="E25">
-        <v>-32.3955005534953</v>
+        <v>-31.84633251058511</v>
       </c>
       <c r="F25">
-        <v>-1.260004124256349</v>
+        <v>-1.1809256868829</v>
       </c>
       <c r="G25">
-        <v>-7.977171135189129</v>
+        <v>-8.001497023811693</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.766881457133799</v>
       </c>
       <c r="E26">
-        <v>-32.64058835950143</v>
+        <v>-31.55275606914185</v>
       </c>
       <c r="F26">
-        <v>-1.046340006582661</v>
+        <v>-1.102520712207927</v>
       </c>
       <c r="G26">
-        <v>-8.090213023173083</v>
+        <v>-7.829838616509404</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.087255144712469</v>
       </c>
       <c r="E27">
-        <v>-33.00942577471517</v>
+        <v>-32.27320911291816</v>
       </c>
       <c r="F27">
-        <v>-1.107982138494584</v>
+        <v>-0.9498948466095204</v>
       </c>
       <c r="G27">
-        <v>-8.109854489857579</v>
+        <v>-8.440909043784698</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.412825009762085</v>
       </c>
       <c r="E28">
-        <v>-33.08487920863097</v>
+        <v>-32.88960461670921</v>
       </c>
       <c r="F28">
-        <v>-1.130554321853467</v>
+        <v>-0.9742645872324791</v>
       </c>
       <c r="G28">
-        <v>-7.865463397057501</v>
+        <v>-8.214663051085365</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.73854889807542</v>
       </c>
       <c r="E29">
-        <v>-33.13164023123418</v>
+        <v>-31.82688724319618</v>
       </c>
       <c r="F29">
-        <v>-1.003597905333012</v>
+        <v>-0.8762264767437548</v>
       </c>
       <c r="G29">
-        <v>-8.132508552982811</v>
+        <v>-7.625789831650885</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.056204503843183</v>
       </c>
       <c r="E30">
-        <v>-32.496279478299</v>
+        <v>-32.30803534227415</v>
       </c>
       <c r="F30">
-        <v>-1.023946750582782</v>
+        <v>-0.9630145295350591</v>
       </c>
       <c r="G30">
-        <v>-8.583288986337672</v>
+        <v>-7.712214933499099</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.362071617536865</v>
       </c>
       <c r="E31">
-        <v>-32.10948213517084</v>
+        <v>-31.7128942312381</v>
       </c>
       <c r="F31">
-        <v>-1.189269831731299</v>
+        <v>-1.226039404006764</v>
       </c>
       <c r="G31">
-        <v>-7.708603128315754</v>
+        <v>-8.551534233524983</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.659323810179069</v>
       </c>
       <c r="E32">
-        <v>-31.66783817909878</v>
+        <v>-31.72028470081861</v>
       </c>
       <c r="F32">
-        <v>-1.229531800976966</v>
+        <v>-1.228232092521974</v>
       </c>
       <c r="G32">
-        <v>-8.057501522699544</v>
+        <v>-7.987890681645289</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.944866203519351</v>
       </c>
       <c r="E33">
-        <v>-32.07365737729616</v>
+        <v>-31.97910963272701</v>
       </c>
       <c r="F33">
-        <v>-1.341757359973438</v>
+        <v>-1.195923278710585</v>
       </c>
       <c r="G33">
-        <v>-8.542966541669349</v>
+        <v>-8.25438628701108</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.220094097949154</v>
       </c>
       <c r="E34">
-        <v>-31.22501002707371</v>
+        <v>-30.37412561069148</v>
       </c>
       <c r="F34">
-        <v>-1.229952611617589</v>
+        <v>-1.160300995287998</v>
       </c>
       <c r="G34">
-        <v>-8.801016945364459</v>
+        <v>-8.386102962382063</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.488933122836217</v>
       </c>
       <c r="E35">
-        <v>-31.36156616077501</v>
+        <v>-30.49554984849615</v>
       </c>
       <c r="F35">
-        <v>-1.039884539412645</v>
+        <v>-1.279070656766585</v>
       </c>
       <c r="G35">
-        <v>-8.732081455600216</v>
+        <v>-8.66605924591053</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.745931774894348</v>
       </c>
       <c r="E36">
-        <v>-30.15715736403598</v>
+        <v>-30.7526924523107</v>
       </c>
       <c r="F36">
-        <v>-1.229894625899393</v>
+        <v>-1.106144819595174</v>
       </c>
       <c r="G36">
-        <v>-8.391456114519064</v>
+        <v>-8.246338350805113</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.993088291335869</v>
       </c>
       <c r="E37">
-        <v>-30.65292790568472</v>
+        <v>-30.17851138321915</v>
       </c>
       <c r="F37">
-        <v>-1.400372637395531</v>
+        <v>-1.294230608605219</v>
       </c>
       <c r="G37">
-        <v>-8.264827747641942</v>
+        <v>-8.509798185911391</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.232253068679809</v>
       </c>
       <c r="E38">
-        <v>-30.29556564360642</v>
+        <v>-29.00555283846338</v>
       </c>
       <c r="F38">
-        <v>-1.491001829833616</v>
+        <v>-1.119701880509391</v>
       </c>
       <c r="G38">
-        <v>-8.94941214916229</v>
+        <v>-8.860014177419812</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.4547483541243</v>
       </c>
       <c r="E39">
-        <v>-29.66592435334293</v>
+        <v>-28.1301988127807</v>
       </c>
       <c r="F39">
-        <v>-1.232109680334478</v>
+        <v>-0.914145822974305</v>
       </c>
       <c r="G39">
-        <v>-9.083111841311297</v>
+        <v>-8.78829782940258</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.663760702555789</v>
       </c>
       <c r="E40">
-        <v>-28.68410363950291</v>
+        <v>-28.80716944913536</v>
       </c>
       <c r="F40">
-        <v>-1.212759017805082</v>
+        <v>-0.7709492635219657</v>
       </c>
       <c r="G40">
-        <v>-8.645139908647876</v>
+        <v>-8.7196205621904</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.858592510279517</v>
       </c>
       <c r="E41">
-        <v>-28.63181787861035</v>
+        <v>-28.09392120750526</v>
       </c>
       <c r="F41">
-        <v>-1.145272753866409</v>
+        <v>-1.084320652001019</v>
       </c>
       <c r="G41">
-        <v>-8.197017843361049</v>
+        <v>-7.940424079703218</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.029405712885392</v>
       </c>
       <c r="E42">
-        <v>-27.78123007727562</v>
+        <v>-27.25584557985372</v>
       </c>
       <c r="F42">
-        <v>-1.279556908432028</v>
+        <v>-1.015965430656809</v>
       </c>
       <c r="G42">
-        <v>-8.621443023677774</v>
+        <v>-7.698347058235091</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.182502021188805</v>
       </c>
       <c r="E43">
-        <v>-28.25654323759471</v>
+        <v>-27.79398678855523</v>
       </c>
       <c r="F43">
-        <v>-1.401234139494442</v>
+        <v>-0.8223527743352862</v>
       </c>
       <c r="G43">
-        <v>-8.664324520047952</v>
+        <v>-8.181670154240988</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.318293512248986</v>
       </c>
       <c r="E44">
-        <v>-26.94194081859003</v>
+        <v>-27.19232920342213</v>
       </c>
       <c r="F44">
-        <v>-1.177093659277549</v>
+        <v>-0.9409004333499235</v>
       </c>
       <c r="G44">
-        <v>-8.580726624090277</v>
+        <v>-8.312499603407447</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.431643934303585</v>
       </c>
       <c r="E45">
-        <v>-26.96035812237922</v>
+        <v>-25.81048800235156</v>
       </c>
       <c r="F45">
-        <v>-1.134056659232504</v>
+        <v>-0.9475654774728482</v>
       </c>
       <c r="G45">
-        <v>-8.176459355562177</v>
+        <v>-8.368858330667999</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.534689069711246</v>
       </c>
       <c r="E46">
-        <v>-25.43448880549469</v>
+        <v>-26.41219540069874</v>
       </c>
       <c r="F46">
-        <v>-1.29325147833511</v>
+        <v>-0.8716290376582175</v>
       </c>
       <c r="G46">
-        <v>-8.145850051506073</v>
+        <v>-8.97157956209325</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.630157311753096</v>
       </c>
       <c r="E47">
-        <v>-25.23680280116385</v>
+        <v>-25.62744255448752</v>
       </c>
       <c r="F47">
-        <v>-1.192664481347972</v>
+        <v>-0.8993014791161378</v>
       </c>
       <c r="G47">
-        <v>-8.52870140094063</v>
+        <v>-9.036562260483604</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.716352925175566</v>
       </c>
       <c r="E48">
-        <v>-24.4037401942388</v>
+        <v>-26.22402372025801</v>
       </c>
       <c r="F48">
-        <v>-1.153742810560034</v>
+        <v>-0.8254939435267019</v>
       </c>
       <c r="G48">
-        <v>-8.43149716281655</v>
+        <v>-8.106653192321103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.805248189560327</v>
       </c>
       <c r="E49">
-        <v>-24.74020128453471</v>
+        <v>-24.35853243822023</v>
       </c>
       <c r="F49">
-        <v>-1.267815628864748</v>
+        <v>-0.8384512664412918</v>
       </c>
       <c r="G49">
-        <v>-8.548501773811012</v>
+        <v>-8.618387390145026</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.896828738524564</v>
       </c>
       <c r="E50">
-        <v>-23.989402936433</v>
+        <v>-23.3720949451294</v>
       </c>
       <c r="F50">
-        <v>-1.135218030331229</v>
+        <v>-0.9822094589927292</v>
       </c>
       <c r="G50">
-        <v>-8.551888461897684</v>
+        <v>-8.013947985584892</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.990880930965644</v>
       </c>
       <c r="E51">
-        <v>-23.36615811570534</v>
+        <v>-23.4909990871488</v>
       </c>
       <c r="F51">
-        <v>-1.077928969121018</v>
+        <v>-0.6841479568522166</v>
       </c>
       <c r="G51">
-        <v>-8.628242884215435</v>
+        <v>-9.075140047652733</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.098648314183631</v>
       </c>
       <c r="E52">
-        <v>-23.18088918710353</v>
+        <v>-22.46895873140966</v>
       </c>
       <c r="F52">
-        <v>-0.8861188402679865</v>
+        <v>-0.9292776103212436</v>
       </c>
       <c r="G52">
-        <v>-8.405744429066559</v>
+        <v>-8.903481640350442</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.218513891694826</v>
       </c>
       <c r="E53">
-        <v>-23.19168506913782</v>
+        <v>-22.10191232766595</v>
       </c>
       <c r="F53">
-        <v>-1.269263615084842</v>
+        <v>-0.7413599798939673</v>
       </c>
       <c r="G53">
-        <v>-8.241385774678362</v>
+        <v>-9.231228959283829</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.352454301631415</v>
       </c>
       <c r="E54">
-        <v>-22.39990403126669</v>
+        <v>-22.47875382068825</v>
       </c>
       <c r="F54">
-        <v>-1.174451167262619</v>
+        <v>-0.6749182872502245</v>
       </c>
       <c r="G54">
-        <v>-8.550256362946824</v>
+        <v>-8.975879960748765</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.509554747381333</v>
       </c>
       <c r="E55">
-        <v>-21.98241495555155</v>
+        <v>-21.68286998536618</v>
       </c>
       <c r="F55">
-        <v>-1.172260963849617</v>
+        <v>-0.9240141638438555</v>
       </c>
       <c r="G55">
-        <v>-8.344883359872597</v>
+        <v>-8.89527148741305</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.683069503886248</v>
       </c>
       <c r="E56">
-        <v>-21.44763840303774</v>
+        <v>-21.01841152269472</v>
       </c>
       <c r="F56">
-        <v>-1.096773499167303</v>
+        <v>-0.8683429041713119</v>
       </c>
       <c r="G56">
-        <v>-8.761512205444337</v>
+        <v>-9.099518905003926</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.873529888888159</v>
       </c>
       <c r="E57">
-        <v>-21.35220081332609</v>
+        <v>-21.08306907457623</v>
       </c>
       <c r="F57">
-        <v>-1.186019318042714</v>
+        <v>-0.6179050723851458</v>
       </c>
       <c r="G57">
-        <v>-9.164842589584824</v>
+        <v>-9.405476213197829</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.083916620317783</v>
       </c>
       <c r="E58">
-        <v>-20.97107085541853</v>
+        <v>-20.56043336087699</v>
       </c>
       <c r="F58">
-        <v>-1.238843478951836</v>
+        <v>-1.215894388424678</v>
       </c>
       <c r="G58">
-        <v>-9.19506787035837</v>
+        <v>-9.920613651836122</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.300725042185935</v>
       </c>
       <c r="E59">
-        <v>-20.29739694814145</v>
+        <v>-20.27568291527468</v>
       </c>
       <c r="F59">
-        <v>-1.356016876445229</v>
+        <v>-1.070029657567922</v>
       </c>
       <c r="G59">
-        <v>-9.153255680197375</v>
+        <v>-9.62768665088479</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.522859122263892</v>
       </c>
       <c r="E60">
-        <v>-20.70740045632192</v>
+        <v>-19.33390523284749</v>
       </c>
       <c r="F60">
-        <v>-1.36789483663397</v>
+        <v>-1.112513308187897</v>
       </c>
       <c r="G60">
-        <v>-9.701160898583375</v>
+        <v>-9.353563548596517</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.747450885192617</v>
       </c>
       <c r="E61">
-        <v>-19.56566347561204</v>
+        <v>-19.45826165757212</v>
       </c>
       <c r="F61">
-        <v>-1.409957676613324</v>
+        <v>-1.143857902342428</v>
       </c>
       <c r="G61">
-        <v>-9.469078414098307</v>
+        <v>-9.555301572668625</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.956019321449023</v>
       </c>
       <c r="E62">
-        <v>-19.39058361352749</v>
+        <v>-19.11396630724295</v>
       </c>
       <c r="F62">
-        <v>-1.681600885543755</v>
+        <v>-1.318430533910604</v>
       </c>
       <c r="G62">
-        <v>-9.279218627421104</v>
+        <v>-9.69895607525422</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.14896310516668</v>
       </c>
       <c r="E63">
-        <v>-19.46770352587811</v>
+        <v>-19.68753829658047</v>
       </c>
       <c r="F63">
-        <v>-1.504585398504723</v>
+        <v>-1.324905053530885</v>
       </c>
       <c r="G63">
-        <v>-9.872369071692322</v>
+        <v>-10.36639516142668</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.3221109020321</v>
       </c>
       <c r="E64">
-        <v>-19.77822551705808</v>
+        <v>-18.09123309498064</v>
       </c>
       <c r="F64">
-        <v>-1.538322317718538</v>
+        <v>-1.29040189446948</v>
       </c>
       <c r="G64">
-        <v>-9.581199970422343</v>
+        <v>-9.972105877153947</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.45887879828787</v>
       </c>
       <c r="E65">
-        <v>-19.22279006612128</v>
+        <v>-19.11650225268725</v>
       </c>
       <c r="F65">
-        <v>-1.540592044402209</v>
+        <v>-1.47770239118167</v>
       </c>
       <c r="G65">
-        <v>-10.05500855854837</v>
+        <v>-10.96284621960056</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.56594029799862</v>
       </c>
       <c r="E66">
-        <v>-18.18317923123238</v>
+        <v>-18.05619176310929</v>
       </c>
       <c r="F66">
-        <v>-1.608388117749529</v>
+        <v>-1.653378408130375</v>
       </c>
       <c r="G66">
-        <v>-10.02430655921717</v>
+        <v>-10.35768511611286</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.64119863894181</v>
       </c>
       <c r="E67">
-        <v>-18.18275808314967</v>
+        <v>-18.40079052119697</v>
       </c>
       <c r="F67">
-        <v>-2.071709745115945</v>
+        <v>-1.59167911886766</v>
       </c>
       <c r="G67">
-        <v>-10.00451611798341</v>
+        <v>-10.03073894919998</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.6725504792031</v>
       </c>
       <c r="E68">
-        <v>-19.3741180820356</v>
+        <v>-17.95387089290598</v>
       </c>
       <c r="F68">
-        <v>-1.948272233322583</v>
+        <v>-1.487149093043196</v>
       </c>
       <c r="G68">
-        <v>-9.853214255202101</v>
+        <v>-10.57888914795588</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.67012013864281</v>
       </c>
       <c r="E69">
-        <v>-18.88852981419311</v>
+        <v>-17.94021754377285</v>
       </c>
       <c r="F69">
-        <v>-2.127192137020651</v>
+        <v>-1.707985215690322</v>
       </c>
       <c r="G69">
-        <v>-9.999321872032294</v>
+        <v>-10.01022680903865</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.63035378440476</v>
       </c>
       <c r="E70">
-        <v>-18.68719385981208</v>
+        <v>-18.18345093967284</v>
       </c>
       <c r="F70">
-        <v>-2.302752182532964</v>
+        <v>-1.837819380568102</v>
       </c>
       <c r="G70">
-        <v>-9.89904875819331</v>
+        <v>-9.883992397080704</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.5451234726728</v>
       </c>
       <c r="E71">
-        <v>-18.28324492137987</v>
+        <v>-17.64778680625353</v>
       </c>
       <c r="F71">
-        <v>-2.20426758201413</v>
+        <v>-2.072314453319989</v>
       </c>
       <c r="G71">
-        <v>-9.681304246438826</v>
+        <v>-9.707388034742744</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.42457680609074</v>
       </c>
       <c r="E72">
-        <v>-18.36714395931998</v>
+        <v>-17.72441764341133</v>
       </c>
       <c r="F72">
-        <v>-2.085537682170878</v>
+        <v>-2.181279558219042</v>
       </c>
       <c r="G72">
-        <v>-9.780759655529611</v>
+        <v>-9.614977466559527</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.26549410970944</v>
       </c>
       <c r="E73">
-        <v>-18.18577857531278</v>
+        <v>-18.3481424823838</v>
       </c>
       <c r="F73">
-        <v>-2.211419706169901</v>
+        <v>-1.918022740874553</v>
       </c>
       <c r="G73">
-        <v>-9.705785730701736</v>
+        <v>-9.871329560392992</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.06641906202278</v>
       </c>
       <c r="E74">
-        <v>-18.60656438010551</v>
+        <v>-18.17665370018733</v>
       </c>
       <c r="F74">
-        <v>-2.296522031296509</v>
+        <v>-2.197631530750304</v>
       </c>
       <c r="G74">
-        <v>-9.505160049930824</v>
+        <v>-10.0330000518033</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.840227153567676</v>
       </c>
       <c r="E75">
-        <v>-19.22949220765263</v>
+        <v>-18.05467472431672</v>
       </c>
       <c r="F75">
-        <v>-2.481975268700456</v>
+        <v>-2.44869975013</v>
       </c>
       <c r="G75">
-        <v>-9.018804494210954</v>
+        <v>-9.676447676132716</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.586852765715154</v>
       </c>
       <c r="E76">
-        <v>-19.21934842587545</v>
+        <v>-18.62109172472212</v>
       </c>
       <c r="F76">
-        <v>-2.565337193913782</v>
+        <v>-2.198295881407349</v>
       </c>
       <c r="G76">
-        <v>-9.634529548514463</v>
+        <v>-9.125635798763236</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.312405009698791</v>
       </c>
       <c r="E77">
-        <v>-19.00683619764349</v>
+        <v>-19.55854924294599</v>
       </c>
       <c r="F77">
-        <v>-2.754645653210359</v>
+        <v>-2.281053926784034</v>
       </c>
       <c r="G77">
-        <v>-9.408747032190629</v>
+        <v>-9.260917931680014</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.031437262091863</v>
       </c>
       <c r="E78">
-        <v>-19.96401974864478</v>
+        <v>-19.48200444679434</v>
       </c>
       <c r="F78">
-        <v>-2.685994704703349</v>
+        <v>-2.447705709246641</v>
       </c>
       <c r="G78">
-        <v>-9.371212066866372</v>
+        <v>-9.568404711913061</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.743924725832704</v>
       </c>
       <c r="E79">
-        <v>-20.18134574474689</v>
+        <v>-19.56163313374521</v>
       </c>
       <c r="F79">
-        <v>-2.547924082739534</v>
+        <v>-2.465233135122475</v>
       </c>
       <c r="G79">
-        <v>-8.623316792453</v>
+        <v>-8.882936394733726</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.459320630760057</v>
       </c>
       <c r="E80">
-        <v>-20.48710378127078</v>
+        <v>-19.98236459684985</v>
       </c>
       <c r="F80">
-        <v>-2.757183770932536</v>
+        <v>-2.871991351123534</v>
       </c>
       <c r="G80">
-        <v>-8.698966068570886</v>
+        <v>-8.610591055400041</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.191102983034062</v>
       </c>
       <c r="E81">
-        <v>-21.2475296651128</v>
+        <v>-20.14051702309373</v>
       </c>
       <c r="F81">
-        <v>-2.800757553054596</v>
+        <v>-2.406508513203213</v>
       </c>
       <c r="G81">
-        <v>-8.158284460551577</v>
+        <v>-8.720087349111436</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.939538524392005</v>
       </c>
       <c r="E82">
-        <v>-21.35011771528256</v>
+        <v>-21.14548956029796</v>
       </c>
       <c r="F82">
-        <v>-2.760377955637731</v>
+        <v>-2.837291040620262</v>
       </c>
       <c r="G82">
-        <v>-8.03039808636953</v>
+        <v>-7.69440088795228</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.718912554239567</v>
       </c>
       <c r="E83">
-        <v>-22.64307855700459</v>
+        <v>-21.94728305420004</v>
       </c>
       <c r="F83">
-        <v>-2.742944135278413</v>
+        <v>-2.710509409621798</v>
       </c>
       <c r="G83">
-        <v>-7.734491594432854</v>
+        <v>-8.423488953157053</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.542842668597937</v>
       </c>
       <c r="E84">
-        <v>-23.24935971409951</v>
+        <v>-22.89573570731454</v>
       </c>
       <c r="F84">
-        <v>-3.143188898391258</v>
+        <v>-2.773727096333845</v>
       </c>
       <c r="G84">
-        <v>-7.931813350755574</v>
+        <v>-7.627080944411201</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.40958139520095</v>
       </c>
       <c r="E85">
-        <v>-23.29152433558493</v>
+        <v>-24.10035507809493</v>
       </c>
       <c r="F85">
-        <v>-3.061570686560826</v>
+        <v>-3.064266194089535</v>
       </c>
       <c r="G85">
-        <v>-8.021006068674618</v>
+        <v>-7.813709638642075</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.332674933703128</v>
       </c>
       <c r="E86">
-        <v>-24.41678672785491</v>
+        <v>-24.36237258417874</v>
       </c>
       <c r="F86">
-        <v>-3.383711172365914</v>
+        <v>-2.974320404758759</v>
       </c>
       <c r="G86">
-        <v>-7.686664143027004</v>
+        <v>-7.995978344397728</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.319590800505999</v>
       </c>
       <c r="E87">
-        <v>-26.133685192279</v>
+        <v>-25.70519645319922</v>
       </c>
       <c r="F87">
-        <v>-3.208839500165328</v>
+        <v>-2.971545373959381</v>
       </c>
       <c r="G87">
-        <v>-7.67137273318111</v>
+        <v>-8.137308844014754</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.361203595556686</v>
       </c>
       <c r="E88">
-        <v>-26.33284747913634</v>
+        <v>-26.72961425779238</v>
       </c>
       <c r="F88">
-        <v>-3.195452254568685</v>
+        <v>-3.22944348257516</v>
       </c>
       <c r="G88">
-        <v>-7.502011844483074</v>
+        <v>-7.731320091806232</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.467123196139323</v>
       </c>
       <c r="E89">
-        <v>-28.76913479594494</v>
+        <v>-28.50848488901145</v>
       </c>
       <c r="F89">
-        <v>-3.499539301197161</v>
+        <v>-3.110340817400647</v>
       </c>
       <c r="G89">
-        <v>-7.739924199662799</v>
+        <v>-7.065493241311394</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.636067770498809</v>
       </c>
       <c r="E90">
-        <v>-29.21837300292786</v>
+        <v>-28.87085790757924</v>
       </c>
       <c r="F90">
-        <v>-3.326002128882484</v>
+        <v>-3.391192986748</v>
       </c>
       <c r="G90">
-        <v>-7.895645640739036</v>
+        <v>-7.55790709536813</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.851218363626985</v>
       </c>
       <c r="E91">
-        <v>-30.98570734661238</v>
+        <v>-30.12209565403159</v>
       </c>
       <c r="F91">
-        <v>-3.925541320332654</v>
+        <v>-3.48659357542621</v>
       </c>
       <c r="G91">
-        <v>-7.652032526140688</v>
+        <v>-7.483476100008695</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.114657000939889</v>
       </c>
       <c r="E92">
-        <v>-31.88138289940448</v>
+        <v>-33.03462220409385</v>
       </c>
       <c r="F92">
-        <v>-3.683094748881295</v>
+        <v>-3.31714191114214</v>
       </c>
       <c r="G92">
-        <v>-7.641127589134328</v>
+        <v>-8.068105200061829</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.415399996851596</v>
       </c>
       <c r="E93">
-        <v>-33.72926068178943</v>
+        <v>-34.60359806505739</v>
       </c>
       <c r="F93">
-        <v>-3.5660688007856</v>
+        <v>-3.757930288417605</v>
       </c>
       <c r="G93">
-        <v>-7.646897870009278</v>
+        <v>-7.776237573683064</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.729445516292609</v>
       </c>
       <c r="E94">
-        <v>-35.79166586333974</v>
+        <v>-35.08298232350937</v>
       </c>
       <c r="F94">
-        <v>-3.60610959593472</v>
+        <v>-3.823935431440072</v>
       </c>
       <c r="G94">
-        <v>-8.273915195147241</v>
+        <v>-8.147621193369584</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.053213046564094</v>
       </c>
       <c r="E95">
-        <v>-37.47105950603231</v>
+        <v>-36.0294447122975</v>
       </c>
       <c r="F95">
-        <v>-4.067445626636626</v>
+        <v>-3.61038231499836</v>
       </c>
       <c r="G95">
-        <v>-7.981968115675532</v>
+        <v>-8.391628262887107</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.365767523888017</v>
       </c>
       <c r="E96">
-        <v>-38.24290620132167</v>
+        <v>-39.00334793482271</v>
       </c>
       <c r="F96">
-        <v>-3.92665547448942</v>
+        <v>-3.923844823891721</v>
       </c>
       <c r="G96">
-        <v>-8.613242802376998</v>
+        <v>-8.39038349776434</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.643634829537364</v>
       </c>
       <c r="E97">
-        <v>-40.81401751052363</v>
+        <v>-40.24931906600415</v>
       </c>
       <c r="F97">
-        <v>-4.065523814262131</v>
+        <v>-4.3011380113752</v>
       </c>
       <c r="G97">
-        <v>-8.912936558410602</v>
+        <v>-8.486902452961791</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.873181311360995</v>
       </c>
       <c r="E98">
-        <v>-42.77255081952301</v>
+        <v>-42.37257788126954</v>
       </c>
       <c r="F98">
-        <v>-4.318295157021984</v>
+        <v>-4.455986386715318</v>
       </c>
       <c r="G98">
-        <v>-9.389400204059129</v>
+        <v>-9.122417948499065</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.04173167142793</v>
       </c>
       <c r="E99">
-        <v>-44.86935202539858</v>
+        <v>-43.71560779585737</v>
       </c>
       <c r="F99">
-        <v>-4.216453183419604</v>
+        <v>-4.199544547993661</v>
       </c>
       <c r="G99">
-        <v>-9.281019564194468</v>
+        <v>-9.393674118350328</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.11707078078822</v>
       </c>
       <c r="E100">
-        <v>-46.46594931357191</v>
+        <v>-46.62665353491911</v>
       </c>
       <c r="F100">
-        <v>-4.289706541216567</v>
+        <v>-4.646220132400821</v>
       </c>
       <c r="G100">
-        <v>-9.256299720652731</v>
+        <v>-9.995786209396353</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.11693811333908</v>
       </c>
       <c r="E101">
-        <v>-48.46095834858457</v>
+        <v>-47.86919208280273</v>
       </c>
       <c r="F101">
-        <v>-4.611808922121127</v>
+        <v>-4.362069404055521</v>
       </c>
       <c r="G101">
-        <v>-9.859961147011134</v>
+        <v>-9.53566010598413</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.995883955958353</v>
       </c>
       <c r="E102">
-        <v>-50.31777986713467</v>
+        <v>-50.2299489816374</v>
       </c>
       <c r="F102">
-        <v>-4.658817115495193</v>
+        <v>-4.680599036351806</v>
       </c>
       <c r="G102">
-        <v>-9.920696415474604</v>
+        <v>-10.4112861589392</v>
       </c>
     </row>
   </sheetData>
